--- a/光伏配储项目/电价数据/2026/梨园站.xlsx
+++ b/光伏配储项目/电价数据/2026/梨园站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51303</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75501</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57653</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59401</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5265599999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51476</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42094</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44531</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12522</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11483</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10521</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10096</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15155</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10801</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.06805</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21553</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.47567</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23118</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.20384</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.03079</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.60589</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.61483</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53289</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.3451</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59028</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57198</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.62253</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.81336</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6315700000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.77306</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.07458</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67426</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5934299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7950199999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.7449600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6479600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61441</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5273600000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48124</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42616</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70204</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.84126</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.76094</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91384</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54665</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50727</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49762</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60766</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8141699999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.44815</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51522</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49575</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.08192</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.68247</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.83789</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.77203</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.69575</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.76524</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.54932</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.92175</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.86824</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50271</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5384500000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.02351</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6876100000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.60772</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.6078300000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.60246</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.61725</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.80436</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.5845499999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6365499999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7924</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67928</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8175</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73268</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.67326</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.63018</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7735599999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.53527</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.19995</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.72337</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5154500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5006700000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.56241</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21771</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56164</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5067699999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.07609</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.63102</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.66146</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50818</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.5811499999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6544099999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6684</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.65024</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5598099999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.58911</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.95455</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5502400000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62918</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.66291</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5817599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51084</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34223</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52874</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.54945</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22358</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5097699999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.43562</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.19005</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.52923</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45951</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13693</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.25581</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.76705</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32965</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4665899999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03426</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18508</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22592</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.16142</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04059</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21831</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05572</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00166</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04885</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10771</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35039</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66755</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.7712100000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.07665000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.11257</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04425</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.18846</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.18689</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04782</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19989</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.1428</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33517</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31718</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17238</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15862</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50771</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78106</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92048</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49462</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91484</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8643200000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29726</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88922</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63198</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5339299999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33257</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03412</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53247</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79238</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52834</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77438</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77865</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87695</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87459</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49445</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40161</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20872</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8789400000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5510900000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6235599999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53876</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49821</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58433</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59517</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66864</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41759</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87174</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.89495</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.84839</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86354</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44113</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.73482</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35302</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9147999999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46257</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16739</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26253</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19019</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5922799999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8889600000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.5868</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14098</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6972</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78728</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6472899999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57399</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.59574</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.5326799999999999</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.7689600000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.76548</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32267</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.49858</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24623</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16096</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16777</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14669</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15054</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14709</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15039</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14951</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27754</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15165</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.16881</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11882</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11817</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15059</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15592</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43597</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34762</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53347</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46518</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27166</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24436</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24941</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3592</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.51275</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43593</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.67622</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.83785</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.81145</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.73783</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.94031</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6212799999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69494</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52106</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.35044</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.46987</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34917</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76276</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34405</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6364500000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60288</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59593</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46537</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6979500000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47461</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.81138</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.48524</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4704100000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35931</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48741</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53179</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.51579</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6919099999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49583</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.84482</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65646</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.58288</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49054</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50741</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54173</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69224</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7196900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.62682</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80506</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58566</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83441</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77738</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62599</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67625</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46896</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55248</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45461</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43529</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45308</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20758</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.3471</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11247</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36341</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22375</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25021</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13738</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04259</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17146</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18531</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23168</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25338</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23322</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34798</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17042</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21606</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23568</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02465</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11807</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03921</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01424</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03861</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03545</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04765999999999999</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02478</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02418</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03088</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04175</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18848</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20747</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27674</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16939</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.70602</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6104400000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.19859</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25474</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23953</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25964</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24023</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.19429</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7307</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6729299999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.69179</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.71641</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18979</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.21296</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25598</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.15312</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.11498</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00822</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07761</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.19272</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02198</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.15246</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.15763</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.005849999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12969</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.14203</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13887</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32204</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.75836</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.49489</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45424</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.53183</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44679</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.5362100000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.35169</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.20499</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.69426</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.6399900000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.48192</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5131699999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.54098</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.23697</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36822</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.48571</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51359</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5864199999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5957100000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.48377</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7444299999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9781799999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.60607</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6023200000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37265</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21274</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16644</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07199</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20047</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16546</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16413</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06019</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06849</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08226</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08541</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06067</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18755</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17318</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36276</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.90261</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.49574</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.70886</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.02056</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.69557</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.15467</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.75402</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.53813</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.66889</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6608099999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49189</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.51689</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.69037</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.53875</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24386</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.12256</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.18877</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.03438</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5475800000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.11048</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.50658</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18462</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.21354</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12944</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.13792</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.6309400000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12515</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19886</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47524</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37071</v>
       </c>
     </row>
   </sheetData>
